--- a/horarios-141-2026-01-06.xlsx
+++ b/horarios-141-2026-01-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,11 +457,16 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 19:10:59</t>
+          <t>Última actualización: 19:31:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,11 +487,12 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 18 filas</t>
+          <t>Ejecuciones: 35 filas únicas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,6 +513,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,6 +539,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -557,6 +565,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -582,6 +591,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -607,6 +617,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -632,6 +643,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -657,6 +669,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -682,6 +695,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -707,6 +721,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -732,6 +747,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -757,6 +773,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -782,6 +799,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -807,6 +825,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -832,6 +851,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -857,6 +877,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -882,6 +903,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -905,6 +927,449 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>29</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>39</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>42</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>53</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>82</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>85</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>86</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>94</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>97</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,11 +1413,16 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 19:10:59</t>
+          <t>Última actualización: 19:31:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -973,11 +1443,12 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas</t>
+          <t>Ejecuciones: 5 filas únicas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -996,6 +1467,85 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>53</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>97</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,11 +1589,16 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 19:10:59</t>
+          <t>Última actualización: 19:31:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1064,11 +1619,12 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1087,6 +1643,33 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19:31:08</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-06.xlsx
+++ b/horarios-141-2026-01-06.xlsx
@@ -59,10 +59,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,128 +437,71 @@
           <t>LÍNEA 141 - LP1912 - 06/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Última actualización: 19:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Filas únicas: 38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912 - 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Última actualización: 19:31:13</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ejecuciones: 35 filas únicas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>19:16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>27_EL RETIRO</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>19:10:48</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19:10:48</t>
+          <t>Última actualización: 19:31:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -570,21 +513,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:10:48</t>
+          <t>Ejecuciones: 35 filas únicas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -601,16 +544,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -627,16 +570,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -653,16 +596,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -679,16 +622,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -705,16 +648,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -731,16 +674,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -757,16 +700,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -783,16 +726,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -809,16 +752,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -835,16 +778,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -861,16 +804,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -887,16 +830,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -913,116 +856,116 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>66</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19:10:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>70</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19:10:48</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>72</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19:10:48</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>20:23</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D22" t="n">
         <v>73</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>9</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>19:41</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>14</v>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11X44_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1039,16 +982,16 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1065,16 +1008,16 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1091,16 +1034,16 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>11X44_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1117,16 +1060,16 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1143,16 +1086,16 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1169,16 +1112,16 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1195,16 +1138,16 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1221,16 +1164,16 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1247,7 +1190,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1256,7 +1199,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1273,16 +1216,16 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1299,16 +1242,16 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1325,16 +1268,16 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1351,25 +1294,181 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>85</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>86</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>94</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>21:08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D39" t="n">
         <v>97</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>19:39:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>19:39:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>44</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>19:39:07</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,157 +1492,178 @@
           <t>LÍNEA 141 - LP1912-215 - 06/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Última actualización: 19:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Filas únicas: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215 - 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Última actualización: 19:31:13</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>19:39</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D5" t="n">
         <v>29</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ejecuciones: 5 filas únicas</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>20:23</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D6" t="n">
         <v>73</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
         <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D7" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
         <is>
           <t>20:24</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D8" t="n">
         <v>53</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19:31:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>21:08</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>97</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>19:31:02</t>
         </is>
@@ -1560,7 +1680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,107 +1689,154 @@
           <t>LÍNEA 141 - 6203-6173 - 06/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Última actualización: 19:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Filas únicas: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173 - 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Última actualización: 19:31:13</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>19:53</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D5" t="n">
         <v>43</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>20:39</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D6" t="n">
         <v>89</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
         <is>
           <t>19:54</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D7" t="n">
         <v>23</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>19:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>62</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19:39:17</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-06.xlsx
+++ b/horarios-141-2026-01-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
     </row>
@@ -485,25 +485,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -512,7 +537,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:39:17</t>
+          <t>Última actualización: 19:41:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -525,6 +550,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -533,25 +563,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -564,25 +599,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>19:51</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11X44_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -595,25 +635,30 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>19:51</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16_P MOR-SANTA ANA</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -626,25 +671,30 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>81_EL PELIGRO</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -657,25 +707,30 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>24</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -688,25 +743,30 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -719,25 +779,30 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>26</v>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -750,25 +815,30 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>27</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -781,25 +851,30 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>20:21</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>56</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -812,25 +887,30 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>20:23</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>42</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>71</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -843,25 +923,30 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>43</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>84</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -874,25 +959,30 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>72</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>86</v>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -905,25 +995,30 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>21:05</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>84</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>86</v>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -936,25 +1031,30 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>87</v>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>96</v>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -971,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,7 +1084,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1128,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1055,7 +1180,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:39:17</t>
+          <t>Última actualización: 19:41:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1068,6 +1193,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1076,25 +1206,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>27</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1107,25 +1242,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>19:41:11</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>19:56:37</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>87</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>71</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1142,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,7 +1295,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1339,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1226,7 +1391,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:39:17</t>
+          <t>Última actualización: 19:41:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1239,6 +1404,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1247,27 +1417,32 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>19:41:16</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>19:54</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>L6203</t>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>19:56:48</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>44</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>
@@ -1278,27 +1453,32 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>19:41:22</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>59</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>L6173</t>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>19:56:43</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>92</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-06.xlsx
+++ b/horarios-141-2026-01-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
     </row>
@@ -510,25 +510,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -537,7 +562,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -555,6 +580,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -568,25 +598,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>19:59</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -604,25 +639,30 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>13</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -640,25 +680,30 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>14</v>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -676,25 +721,30 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>20:12</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>23_HERNANDEZ</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>16</v>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="n">
+        <v>23</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -712,25 +762,30 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>24</v>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>27</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -748,25 +803,30 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>26</v>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>38</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -784,25 +844,30 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>26</v>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>51</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -820,25 +885,30 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>20:23</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>27</v>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>53</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -856,25 +926,30 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>20:52</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>56</v>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>53</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -892,25 +967,30 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>21:07</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>71</v>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>63</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -928,25 +1008,30 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>21:20</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>84</v>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -964,25 +1049,30 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>21:22</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>10_OLMOS</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>86</v>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="n">
+        <v>83</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1000,25 +1090,30 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>21:22</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>86</v>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>98</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1036,25 +1131,30 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>21:32</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>96</v>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>99</v>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1071,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,7 +1184,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
     </row>
@@ -1153,25 +1253,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1180,7 +1305,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1198,6 +1323,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1211,25 +1341,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>20:23</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>27</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>38</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1247,25 +1382,30 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>19:56:37</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>21:07</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>71</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>20:29:39</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>78</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1282,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,14 +1435,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 3</t>
+          <t>Filas únicas: 4</t>
         </is>
       </c>
     </row>
@@ -1364,25 +1504,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1391,7 +1556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:41:22</t>
+          <t>Última actualización: 19:56:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1409,6 +1574,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1422,25 +1592,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>19:56:48</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20:29:50</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>44</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
@@ -1458,27 +1633,73 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>19:56:43</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>20:29:45</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>21:28</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>92</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>59</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>20:29:50</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>96</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-06.xlsx
+++ b/horarios-141-2026-01-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:29:50</t>
+          <t>Última actualización: 20:46:08</t>
         </is>
       </c>
     </row>
@@ -535,25 +535,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -562,7 +587,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -585,6 +610,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -603,25 +633,30 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>225_GOMEZ</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -644,25 +679,30 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>20:46</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>17</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -685,25 +725,30 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -726,25 +771,30 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>20:52</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>23</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -767,25 +817,30 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>20:56</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>27_EL RETIRO</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>27</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -808,25 +863,30 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>21:07</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>38</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="Y11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -849,25 +909,30 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>21:20</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>26_HERNANDEZ</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>51</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="Y12" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -890,25 +955,30 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>21:22</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>53</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -931,25 +1001,30 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>21:22</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>53</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -972,25 +1047,30 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>21:32</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>63</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1013,25 +1093,30 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>21:47</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>78</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1054,25 +1139,30 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>21:52</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>83</v>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1095,25 +1185,30 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>22:07</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>17_ROMERO</t>
         </is>
       </c>
-      <c r="T18" t="n">
-        <v>98</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="Y18" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1136,25 +1231,30 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>22:08</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="T19" t="n">
-        <v>99</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1171,7 +1271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,7 +1284,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:29:50</t>
+          <t>Última actualización: 20:46:08</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1378,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1305,7 +1430,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1328,6 +1453,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1346,25 +1476,30 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>21:07</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>38</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1387,25 +1522,30 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20:29:39</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>21:47</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>20:45:57</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>78</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1422,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1435,7 +1575,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:29:50</t>
+          <t>Última actualización: 20:46:08</t>
         </is>
       </c>
     </row>
@@ -1529,25 +1669,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1556,7 +1721,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 19:56:48</t>
+          <t>Última actualización: 20:29:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1579,6 +1744,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1597,27 +1767,32 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>20:29:50</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>L6173</t>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20:46:02</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>
@@ -1638,27 +1813,32 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20:29:45</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>21:28</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>59</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>L6203</t>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>20:46:07</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>
@@ -1679,25 +1859,30 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>20:29:50</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>22:05</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>96</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>20:46:07</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
